--- a/Result/profitability/9906.xlsx
+++ b/Result/profitability/9906.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.2</v>
       </c>
       <c r="M2" t="n">
-        <v>1.17625</v>
+        <v>0.7524999999999997</v>
       </c>
       <c r="N2" t="n">
-        <v>26.86875</v>
+        <v>28.02125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.48</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6512499999999998</v>
+        <v>0.3387499999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>24.885</v>
+        <v>25.27625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2712499999999998</v>
+        <v>0.4374999999999998</v>
       </c>
       <c r="N4" t="n">
-        <v>21.3275</v>
+        <v>22.5275</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.43</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4499999999999998</v>
+        <v>0.5462499999999998</v>
       </c>
       <c r="N5" t="n">
-        <v>18.66375</v>
+        <v>21.0425</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4887499999999999</v>
+        <v>0.5987499999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>16.2625</v>
+        <v>18.9175</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5537499999999997</v>
+        <v>0.3349999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>15.22875</v>
+        <v>15.145</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2487499999999998</v>
+        <v>0.09374999999999978</v>
       </c>
       <c r="N8" t="n">
-        <v>10.63375</v>
+        <v>10.7325</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.31</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01374999999999977</v>
+        <v>0.01374999999999978</v>
       </c>
       <c r="N9" t="n">
         <v>7.26</v>
@@ -9768,6 +9768,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9906</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>320</v>
+      </c>
+      <c r="D75" t="n">
+        <v>198</v>
+      </c>
+      <c r="E75" t="n">
+        <v>123</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38.31</v>
+      </c>
+      <c r="G75" t="n">
+        <v>51</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.97%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>44</v>
+      </c>
+      <c r="K75" t="n">
+        <v>30</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.0675</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.5175</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7898089171974523</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.7899999999999991</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.02105543710021318</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.9870331950207469</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
